--- a/output/pdf_financials_xlsx/MARI.xlsx
+++ b/output/pdf_financials_xlsx/MARI.xlsx
@@ -1057,22 +1057,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>17.869</v>
+        <v>-17.869</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>13.709</v>
+        <v>-13.709</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.121</v>
+        <v>-1.121</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.586</v>
+        <v>-3.586</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>19.212</v>
+        <v>-19.212</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>24.816</v>
+        <v>-24.816</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1269,22 +1269,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>17.869</v>
+        <v>-17.869</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>13.709</v>
+        <v>-13.709</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.121</v>
+        <v>-1.121</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.586</v>
+        <v>-3.586</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>19.212</v>
+        <v>-19.212</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>24.816</v>
+        <v>-24.816</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1401,22 +1401,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>17.869</v>
+        <v>-17.869</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>13.709</v>
+        <v>-13.709</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.121</v>
+        <v>-1.121</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.586</v>
+        <v>-3.586</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>19.212</v>
+        <v>-19.212</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>24.816</v>
+        <v>-24.816</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-14.543</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>17.872</v>
+        <v>-17.866</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>13.715</v>
+        <v>-13.703</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.121</v>
+        <v>-1.121</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.756</v>
+        <v>-3.416</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>19.222</v>
+        <v>-19.202</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>24.816</v>
+        <v>-24.816</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1699,22 +1699,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>17.892</v>
+        <v>-17.846</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>13.732</v>
+        <v>-13.686</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.13</v>
+        <v>-1.112</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.768</v>
+        <v>-3.404</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>19.247</v>
+        <v>-19.177</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>24.872</v>
+        <v>-24.76</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1805,22 +1805,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -30841,19 +30841,19 @@
         </is>
       </c>
       <c r="F357" s="5" t="n">
-        <v>13.709</v>
+        <v>-13.709</v>
       </c>
       <c r="G357" s="5" t="n">
-        <v>1.121</v>
+        <v>-1.121</v>
       </c>
       <c r="H357" s="5" t="n">
-        <v>3.586</v>
+        <v>-3.586</v>
       </c>
       <c r="I357" s="5" t="n">
-        <v>19.212</v>
+        <v>-19.212</v>
       </c>
       <c r="J357" s="5" t="n">
-        <v>24.816</v>
+        <v>-24.816</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
@@ -31191,10 +31191,10 @@
         </is>
       </c>
       <c r="I362" s="5" t="n">
-        <v>19.344</v>
+        <v>-19.344</v>
       </c>
       <c r="J362" s="5" t="n">
-        <v>24.321</v>
+        <v>-24.321</v>
       </c>
       <c r="K362" t="inlineStr">
         <is>
@@ -31264,10 +31264,10 @@
         </is>
       </c>
       <c r="I363" s="5" t="n">
-        <v>19.344</v>
+        <v>-19.344</v>
       </c>
       <c r="J363" s="5" t="n">
-        <v>24.321</v>
+        <v>-24.321</v>
       </c>
       <c r="K363" t="inlineStr">
         <is>
@@ -32857,19 +32857,19 @@
         </is>
       </c>
       <c r="E386" s="5" t="n">
-        <v>17.897</v>
+        <v>-17.897</v>
       </c>
       <c r="F386" s="5" t="n">
-        <v>13.745</v>
+        <v>-13.745</v>
       </c>
       <c r="G386" s="5" t="n">
-        <v>0.826</v>
+        <v>-0.826</v>
       </c>
       <c r="H386" s="5" t="n">
-        <v>3.78</v>
+        <v>-3.78</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>19.344</v>
+        <v>-19.344</v>
       </c>
       <c r="J386" t="inlineStr">
         <is>
@@ -32939,10 +32939,10 @@
         </is>
       </c>
       <c r="H387" s="5" t="n">
-        <v>3.78</v>
+        <v>-3.78</v>
       </c>
       <c r="I387" s="5" t="n">
-        <v>19.344</v>
+        <v>-19.344</v>
       </c>
       <c r="J387" t="inlineStr">
         <is>
@@ -37181,10 +37181,10 @@
         </is>
       </c>
       <c r="E448" s="5" t="n">
-        <v>17.869</v>
+        <v>-17.869</v>
       </c>
       <c r="F448" s="5" t="n">
-        <v>13.709</v>
+        <v>-13.709</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MARI.xlsx
+++ b/output/pdf_financials_xlsx/MARI.xlsx
@@ -1939,16 +1939,16 @@
         <v>9.865</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>26.786</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>14.636</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>16.692</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>22.648</v>
       </c>
     </row>
     <row r="35">
@@ -2019,16 +2019,16 @@
         <v>9.865</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>26.786</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>14.636</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>16.692</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>22.648</v>
       </c>
     </row>
     <row r="37">
@@ -2499,16 +2499,16 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>38.597</v>
+        <v>11.811</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>15.53</v>
+        <v>0.894</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>17.051</v>
+        <v>0.359</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>23.16</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="49">
@@ -5531,31 +5531,31 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.077</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.443</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.199</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.092</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.036</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.052</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.083</v>
       </c>
     </row>
     <row r="125">
@@ -5571,31 +5571,31 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.077</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.443</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.199</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.092</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.036</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.052</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.083</v>
       </c>
     </row>
     <row r="126">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -18024,7 +18024,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -22174,7 +22178,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -23077,7 +23085,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -24481,7 +24493,11 @@
           <t>Finance lease payments (note 9)</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -25110,7 +25126,11 @@
           <t>Finance lease payment (note 11)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -26163,7 +26183,11 @@
           <t>Finance lease payment (note 12)</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MARI.xlsx
+++ b/output/pdf_financials_xlsx/MARI.xlsx
@@ -5365,16 +5365,16 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.974</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.868</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>13.181</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -25199,7 +25199,11 @@
           <t>Issuance of common shares (net of issuance costs) (note 13)</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -26258,7 +26262,11 @@
           <t>Issuance of common shares (net of issuance costs)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -26966,7 +26974,11 @@
           <t>Issuance of common shares (net of issue costs)</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E301" s="5" t="n">
         <v>0.974</v>
       </c>

--- a/output/pdf_financials_xlsx/MARI.xlsx
+++ b/output/pdf_financials_xlsx/MARI.xlsx
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-2.161</v>
+        <v>-4.848</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-7.113</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>2.687</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -1421,10 +1421,8 @@
       <c r="H23" s="3" t="n">
         <v>-14.543</v>
       </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="3" t="n">
+        <v>-17.48</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-2.161</v>
@@ -2047,10 +2045,10 @@
         <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>3.138</v>
@@ -2207,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>3.138</v>
@@ -2487,10 +2485,10 @@
         <v>0.422</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.296</v>
+        <v>1.149</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.299</v>
+        <v>3.156</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -3143,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.203</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.407</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>3.292</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.00645</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>2.891</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.073</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0</v>
@@ -3263,22 +3261,22 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.004368</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.713</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -3407,10 +3405,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="71">
@@ -3447,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="72">
@@ -3607,10 +3605,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3817,12 +3815,10 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.0004555326023624133</v>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001356004025636951</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.0004106701223796965</v>
       </c>
     </row>
     <row r="81">
@@ -4543,13 +4539,11 @@
       <c r="H99" s="3" t="n">
         <v>-14.543</v>
       </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="3" t="n">
+        <v>-17.48</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-2.161</v>
+        <v>-4.848</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-7.113</v>
@@ -4845,25 +4839,25 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.785</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>8.08</v>
@@ -4977,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -6815,7 +6809,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -17153,7 +17151,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -17882,7 +17884,11 @@
           <t>Issuance of common shares under Private Placement (Note 8 (c))</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -19950,7 +19956,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -21098,7 +21108,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E217" s="5" t="n">
         <v>0.387</v>
       </c>
@@ -24148,7 +24162,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -29890,7 +29908,11 @@
           <t>Loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -29959,7 +29981,11 @@
           <t>Income from discontinued operations (Note 5(a))</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
